--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>101266</v>
       </c>
       <c r="B2" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700648.7687457944</v>
+        <v>700649</v>
       </c>
       <c r="R2" t="n">
-        <v>7154705.339495968</v>
+        <v>7154705</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-10-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per-anders Blomqvist, Andreas Garpebring, Sören Uppsäll, Henrik Sporrong, Per Nihlen</t>
+          <t>Per-anders Blomqvist, Andreas Garpebring, Sören Uppsäll, Henrik Sporrong, Per Nihlén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +780,7 @@
         <v>1047558</v>
       </c>
       <c r="B3" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,12 +797,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700642.0791824912</v>
+        <v>700642</v>
       </c>
       <c r="R3" t="n">
-        <v>7154530.484588708</v>
+        <v>7154530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2011-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-10-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,69 +872,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per-anders Blomqvist, Andreas Garpebring, Sören Uppsäll, Henrik Sporrong, Per Nihlen</t>
+          <t>Per-anders Blomqvist, Andreas Garpebring, Sören Uppsäll, Henrik Sporrong, Per Nihlén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106542601</v>
+        <v>119719064</v>
       </c>
       <c r="B4" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ö Ekorrsele NR, Ekorrsele, Vb</t>
+          <t>Ekorrsele NR, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700642.0686543257</v>
+        <v>700570</v>
       </c>
       <c r="R4" t="n">
-        <v>7154675.469368722</v>
+        <v>7154758</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,22 +958,128 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106542601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö Ekorrsele NR, Ekorrsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>700642</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7154675</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Henrik Sporrong</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Henrik Sporrong</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101266</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1047558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719064</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106542601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106542601</v>
+        <v>136183381</v>
       </c>
       <c r="B5" t="n">
-        <v>8455</v>
+        <v>79468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,46 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ö Ekorrsele NR, Ekorrsele, Vb</t>
+          <t>Brännheden, Ekorrsele NR, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700642</v>
+        <v>700630</v>
       </c>
       <c r="R5" t="n">
-        <v>7154675</v>
+        <v>7154854</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,25 +1075,472 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136183381</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106542601</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ö Ekorrsele NR, Ekorrsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>700642</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7154675</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/106542601</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136183380</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brännheden, Ekorrsele NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>700625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7154862</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136183380</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136183383</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brännheden, Ekorrsele NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>700625</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7154730</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136183383</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136183384</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brännheden, Ekorrsele NR, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>700580</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7154758</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>död tall</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136183384</t>
         </is>
       </c>
     </row>
@@ -1112,6 +1550,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136183381</v>
       </c>
       <c r="B5" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136183381</v>
       </c>
       <c r="B5" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61824-2022 artfynd.xlsx
+++ b/artfynd/A 61824-2022 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>136183381</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
